--- a/projects/project-3/assignment/src/data/ccom-qudt-structural-matches-with-defs.xlsx
+++ b/projects/project-3/assignment/src/data/ccom-qudt-structural-matches-with-defs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,6 +468,2950 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ThermodynamicsUnit</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Thermodynamics Unit</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#PhysicalUnit</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Physical Unit</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#BiomedicalUnit</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Biomedical Unit</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ScienceAndEngineeringUnit</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Science And Engineering Unit</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#FinancialUnit</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Financial Unit</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#RadiologyUnit</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Radiology Unit</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#CurrencyUnit</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Currency Unit</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>R:card; R:has</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ElectricityAndMagnetismUnit</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Electricity And Magnetism Unit</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ChemistryUnit</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Chemistry Unit</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#SpaceAndTimeUnit</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Space And Time Unit</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ComputingUnit</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Computing Unit</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#MechanicsUnit</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mechanics Unit</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#HumanUnit</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Human Unit</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#AtomicPhysicsUnit</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Atomic Physics Unit</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001290</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Length</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#CommunicationsUnit</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Communications Unit</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of one-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ThermodynamicsUnit</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Thermodynamics Unit</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#PhysicalUnit</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Physical Unit</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#BiomedicalUnit</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Biomedical Unit</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ScienceAndEngineeringUnit</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Science And Engineering Unit</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#FinancialUnit</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Financial Unit</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#RadiologyUnit</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Radiology Unit</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#CurrencyUnit</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Currency Unit</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>R:card; R:has</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ElectricityAndMagnetismUnit</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Electricity And Magnetism Unit</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ChemistryUnit</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Chemistry Unit</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#SpaceAndTimeUnit</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Space And Time Unit</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ComputingUnit</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Computing Unit</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#MechanicsUnit</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mechanics Unit</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#HumanUnit</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Human Unit</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#AtomicPhysicsUnit</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Atomic Physics Unit</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000217</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Area</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000009</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#CommunicationsUnit</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Communications Unit</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of two-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ThermodynamicsUnit</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Thermodynamics Unit</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#PhysicalUnit</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Physical Unit</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#BiomedicalUnit</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Biomedical Unit</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ScienceAndEngineeringUnit</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Science And Engineering Unit</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#FinancialUnit</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Financial Unit</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#RadiologyUnit</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Radiology Unit</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#CurrencyUnit</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Currency Unit</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>R:card; R:has</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ElectricityAndMagnetismUnit</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Electricity And Magnetism Unit</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ChemistryUnit</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Chemistry Unit</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#SpaceAndTimeUnit</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Space And Time Unit</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ComputingUnit</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Computing Unit</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#MechanicsUnit</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mechanics Unit</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#HumanUnit</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Human Unit</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#AtomicPhysicsUnit</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Atomic Physics Unit</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001357</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Time</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some obo:BFO_0000008</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#CommunicationsUnit</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Communications Unit</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of temporal regions.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ThermodynamicsUnit</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Thermodynamics Unit</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UTD</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Thermodynamics units are units that provide reference scales for quantifying the conversion of energy into work, as well as heat and its relation to macroscopic variables such as temperature and pressure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#PhysicalUnit</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Physical Unit</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UPHS</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#BiomedicalUnit</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Biomedical Unit</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UBM</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ScienceAndEngineeringUnit</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Science And Engineering Unit</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:Unit | SubClassOf: qudt-v1:typePrefix value USE</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#FinancialUnit</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Financial Unit</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UF</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>This class contains units that measure financial quantities, such as currency, transactions, rates of return, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#RadiologyUnit</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Radiology Unit</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UROY</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#CurrencyUnit</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Currency Unit</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>R:card; R:has</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:FinancialUnit | SubClassOf: qudt-v1:currencyExponent exactly 1 | SubClassOf: qudt-v1:typePrefix value UFC</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ElectricityAndMagnetismUnit</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Electricity And Magnetism Unit</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UEM</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>The class of units used to measure the properties of electricity and magnetism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ChemistryUnit</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Chemistry Unit</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UCHM</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#SpaceAndTimeUnit</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Space And Time Unit</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UST</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#ComputingUnit</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Computing Unit</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCPG</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#MechanicsUnit</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mechanics Unit</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UMH</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#HumanUnit</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Human Unit</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ResourceUnit | SubClassOf: qudt-v1:typePrefix value UH</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>units for measuring human resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#AtomicPhysicsUnit</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Atomic Physics Unit</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:PhysicalUnit | SubClassOf: qudt-v1:typePrefix value UAP</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001317</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Measurement Unit of Volume</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>R:some</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SubClassOf: cco:ont00000120 | SubClassOf: cco:ont00001966 some (obo:BFO_0000028 OR obo:BFO_0000029)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>http://qudt.org/schema/qudt#CommunicationsUnit</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Communications Unit</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>R:has</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>SubClassOf: qudt-v1:ScienceAndEngineeringUnit | SubClassOf: qudt-v1:typePrefix value UCMN</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>A Measurement Unit that is used as a standard for measurement of sites or three-dimensional regions or Geospatial Regions.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
